--- a/Currency conversion table.xlsx
+++ b/Currency conversion table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://goodyearcorp-my.sharepoint.com/personal/julien_bechoux_goodyear_com/Documents/Desktop/AI/EMEA Freight Cost Tracker/JulienTest2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{4C788501-D4D4-4928-BE8D-7A488BC12D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61A16427-AE82-4A3B-8E9A-AB1058CBEEAB}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{4C788501-D4D4-4928-BE8D-7A488BC12D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DA6AD84-D8B1-432C-9A01-C41333C991B1}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,30 +33,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Currency</t>
   </si>
   <si>
-    <t>PLN → EUR</t>
-  </si>
-  <si>
-    <t>RSD → EUR</t>
-  </si>
-  <si>
-    <t>TRY → EUR</t>
-  </si>
-  <si>
-    <t>USD → EUR</t>
-  </si>
-  <si>
-    <t>ZAR → EUR</t>
-  </si>
-  <si>
-    <t>Source: valutafx.com</t>
-  </si>
-  <si>
-    <t>Conversion to EUR</t>
+    <t>PLN</t>
+  </si>
+  <si>
+    <t>RSD</t>
+  </si>
+  <si>
+    <t>TRY</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>ZAR</t>
+  </si>
+  <si>
+    <t>Conversion Rate</t>
   </si>
 </sst>
 </file>
@@ -83,7 +80,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -91,96 +88,22 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -516,77 +439,79 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E04CC58B-20AE-40F1-B34F-E8C4186D362D}">
-  <dimension ref="B3:C10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B4" s="6" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="7"/>
-    </row>
-    <row r="5" spans="2:3" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="B5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B6" s="1" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="3">
+      <c r="B2" s="2">
         <v>0.2359</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B7" s="1" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="3">
+      <c r="B3" s="2">
         <v>8.5000000000000006E-3</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B8" s="1" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="3">
+      <c r="B4" s="2">
         <v>1.9199999999999998E-2</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B9" s="1" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="3">
+      <c r="B5" s="2">
         <v>0.85570000000000002</v>
       </c>
     </row>
-    <row r="10" spans="2:3" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="5">
+      <c r="B6" s="2">
         <v>5.21E-2</v>
       </c>
     </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B4:C4"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>